--- a/Bases_de_Dados/FootyStats/Serbia SuperLiga_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Serbia SuperLiga_20252026.xlsx
@@ -42782,7 +42782,7 @@
         <v>3.04</v>
       </c>
       <c r="AU194" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV194" t="n">
         <v>2</v>
@@ -42794,7 +42794,7 @@
         <v>7</v>
       </c>
       <c r="AY194" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ194" t="n">
         <v>9</v>
@@ -43003,28 +43003,28 @@
         <v>5</v>
       </c>
       <c r="AV195" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW195" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX195" t="n">
         <v>2</v>
       </c>
       <c r="AY195" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ195" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA195" t="n">
         <v>4</v>
       </c>
       <c r="BB195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC195" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD195" t="n">
         <v>1.2</v>
@@ -43227,13 +43227,13 @@
         <v>5</v>
       </c>
       <c r="AX196" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY196" t="n">
         <v>10</v>
       </c>
       <c r="AZ196" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA196" t="n">
         <v>7</v>

--- a/Bases_de_Dados/FootyStats/Serbia SuperLiga_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Serbia SuperLiga_20252026.xlsx
@@ -42788,13 +42788,13 @@
         <v>2</v>
       </c>
       <c r="AW194" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX194" t="n">
         <v>7</v>
       </c>
       <c r="AY194" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ194" t="n">
         <v>9</v>

--- a/Bases_de_Dados/FootyStats/Serbia SuperLiga_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Serbia SuperLiga_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP197"/>
+  <dimension ref="A1:BP201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1132,7 +1132,7 @@
         <v>2.58</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1568,7 +1568,7 @@
         <v>2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ9" t="n">
         <v>0.77</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ12" t="n">
         <v>1.33</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ13" t="n">
         <v>1</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ14" t="n">
         <v>1.25</v>
@@ -3966,7 +3966,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR16" t="n">
         <v>1.22</v>
@@ -4184,7 +4184,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR17" t="n">
         <v>1.37</v>
@@ -4402,7 +4402,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR18" t="n">
         <v>1.49</v>
@@ -6361,7 +6361,7 @@
         <v>1</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ27" t="n">
         <v>1.33</v>
@@ -6579,7 +6579,7 @@
         <v>3</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ28" t="n">
         <v>2.08</v>
@@ -7015,7 +7015,7 @@
         <v>1</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ30" t="n">
         <v>1.25</v>
@@ -7236,7 +7236,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ31" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR31" t="n">
         <v>1.11</v>
@@ -7454,7 +7454,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR32" t="n">
         <v>1.36</v>
@@ -7672,7 +7672,7 @@
         <v>2</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR33" t="n">
         <v>1.78</v>
@@ -7890,7 +7890,7 @@
         <v>2</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR34" t="n">
         <v>1.33</v>
@@ -8105,7 +8105,7 @@
         <v>0.5</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ35" t="n">
         <v>0.33</v>
@@ -9849,7 +9849,7 @@
         <v>0.5</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ43" t="n">
         <v>1</v>
@@ -10067,7 +10067,7 @@
         <v>3</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ44" t="n">
         <v>2.08</v>
@@ -10724,7 +10724,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR47" t="n">
         <v>1.71</v>
@@ -10942,7 +10942,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR48" t="n">
         <v>2.48</v>
@@ -11378,7 +11378,7 @@
         <v>2</v>
       </c>
       <c r="AQ50" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR50" t="n">
         <v>1.86</v>
@@ -11596,7 +11596,7 @@
         <v>2</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR51" t="n">
         <v>1.58</v>
@@ -11811,7 +11811,7 @@
         <v>1.33</v>
       </c>
       <c r="AP52" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ52" t="n">
         <v>0.67</v>
@@ -12029,7 +12029,7 @@
         <v>0.33</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ53" t="n">
         <v>0.67</v>
@@ -13119,7 +13119,7 @@
         <v>0.75</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ58" t="n">
         <v>0.33</v>
@@ -13991,10 +13991,10 @@
         <v>0</v>
       </c>
       <c r="AP62" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ62" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR62" t="n">
         <v>1.91</v>
@@ -14209,10 +14209,10 @@
         <v>1</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ63" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR63" t="n">
         <v>2.37</v>
@@ -14648,7 +14648,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ65" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR65" t="n">
         <v>2.39</v>
@@ -15081,7 +15081,7 @@
         <v>0.25</v>
       </c>
       <c r="AP67" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ67" t="n">
         <v>0.67</v>
@@ -15520,7 +15520,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ69" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR69" t="n">
         <v>0.97</v>
@@ -17697,10 +17697,10 @@
         <v>0.6</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ79" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR79" t="n">
         <v>1.65</v>
@@ -18133,7 +18133,7 @@
         <v>2.25</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ81" t="n">
         <v>1.69</v>
@@ -18790,7 +18790,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ84" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR84" t="n">
         <v>1.62</v>
@@ -19005,10 +19005,10 @@
         <v>0.8</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ85" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR85" t="n">
         <v>1.36</v>
@@ -19223,10 +19223,10 @@
         <v>3</v>
       </c>
       <c r="AP86" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ86" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR86" t="n">
         <v>1.95</v>
@@ -19662,7 +19662,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ88" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR88" t="n">
         <v>1.4</v>
@@ -21185,7 +21185,7 @@
         <v>1.4</v>
       </c>
       <c r="AP95" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ95" t="n">
         <v>1.92</v>
@@ -21624,7 +21624,7 @@
         <v>2</v>
       </c>
       <c r="AQ97" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR97" t="n">
         <v>1.71</v>
@@ -21839,7 +21839,7 @@
         <v>0.2</v>
       </c>
       <c r="AP98" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ98" t="n">
         <v>1</v>
@@ -22057,7 +22057,7 @@
         <v>2.4</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ99" t="n">
         <v>1.69</v>
@@ -22278,7 +22278,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ100" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR100" t="n">
         <v>1.99</v>
@@ -22711,10 +22711,10 @@
         <v>3</v>
       </c>
       <c r="AP102" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ102" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR102" t="n">
         <v>1.7</v>
@@ -22932,7 +22932,7 @@
         <v>2</v>
       </c>
       <c r="AQ103" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR103" t="n">
         <v>1.72</v>
@@ -23150,7 +23150,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ104" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR104" t="n">
         <v>1.48</v>
@@ -24240,7 +24240,7 @@
         <v>2.58</v>
       </c>
       <c r="AQ109" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR109" t="n">
         <v>2.66</v>
@@ -25109,7 +25109,7 @@
         <v>0.33</v>
       </c>
       <c r="AP113" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ113" t="n">
         <v>0.77</v>
@@ -25327,7 +25327,7 @@
         <v>1.67</v>
       </c>
       <c r="AP114" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ114" t="n">
         <v>1.92</v>
@@ -25548,7 +25548,7 @@
         <v>2</v>
       </c>
       <c r="AQ115" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR115" t="n">
         <v>1.63</v>
@@ -25766,7 +25766,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ116" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR116" t="n">
         <v>1.5</v>
@@ -25981,7 +25981,7 @@
         <v>0.17</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ117" t="n">
         <v>1</v>
@@ -26635,7 +26635,7 @@
         <v>0.8</v>
       </c>
       <c r="AP120" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ120" t="n">
         <v>1</v>
@@ -27289,7 +27289,7 @@
         <v>0.71</v>
       </c>
       <c r="AP123" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ123" t="n">
         <v>0.77</v>
@@ -27507,7 +27507,7 @@
         <v>0.29</v>
       </c>
       <c r="AP124" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ124" t="n">
         <v>1</v>
@@ -27728,7 +27728,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ125" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR125" t="n">
         <v>1.38</v>
@@ -27943,7 +27943,7 @@
         <v>1.29</v>
       </c>
       <c r="AP126" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ126" t="n">
         <v>1.33</v>
@@ -28818,7 +28818,7 @@
         <v>2</v>
       </c>
       <c r="AQ130" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR130" t="n">
         <v>1.78</v>
@@ -29254,7 +29254,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ132" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR132" t="n">
         <v>2.12</v>
@@ -29472,7 +29472,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ133" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR133" t="n">
         <v>1.71</v>
@@ -29690,7 +29690,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ134" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR134" t="n">
         <v>1.26</v>
@@ -30559,7 +30559,7 @@
         <v>1.38</v>
       </c>
       <c r="AP138" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ138" t="n">
         <v>1.25</v>
@@ -30777,7 +30777,7 @@
         <v>1.25</v>
       </c>
       <c r="AP139" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ139" t="n">
         <v>1.33</v>
@@ -30995,7 +30995,7 @@
         <v>2.38</v>
       </c>
       <c r="AP140" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ140" t="n">
         <v>2.08</v>
@@ -31649,7 +31649,7 @@
         <v>0.71</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ143" t="n">
         <v>1</v>
@@ -32088,7 +32088,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ145" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR145" t="n">
         <v>1.55</v>
@@ -32303,10 +32303,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ146" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR146" t="n">
         <v>2.09</v>
@@ -33178,7 +33178,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ150" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR150" t="n">
         <v>1.06</v>
@@ -33614,7 +33614,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ152" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR152" t="n">
         <v>1.68</v>
@@ -33829,7 +33829,7 @@
         <v>1</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ153" t="n">
         <v>1</v>
@@ -34047,7 +34047,7 @@
         <v>1.22</v>
       </c>
       <c r="AP154" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ154" t="n">
         <v>1.25</v>
@@ -34701,7 +34701,7 @@
         <v>2.44</v>
       </c>
       <c r="AP157" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ157" t="n">
         <v>2.08</v>
@@ -35573,7 +35573,7 @@
         <v>0.89</v>
       </c>
       <c r="AP161" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ161" t="n">
         <v>1</v>
@@ -35791,10 +35791,10 @@
         <v>0.6</v>
       </c>
       <c r="AP162" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ162" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR162" t="n">
         <v>1.56</v>
@@ -36009,7 +36009,7 @@
         <v>0.8</v>
       </c>
       <c r="AP163" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ163" t="n">
         <v>0.67</v>
@@ -36448,7 +36448,7 @@
         <v>2</v>
       </c>
       <c r="AQ165" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR165" t="n">
         <v>1.54</v>
@@ -36884,7 +36884,7 @@
         <v>2</v>
       </c>
       <c r="AQ167" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR167" t="n">
         <v>1.78</v>
@@ -37320,7 +37320,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ169" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR169" t="n">
         <v>1.49</v>
@@ -38189,7 +38189,7 @@
         <v>1.1</v>
       </c>
       <c r="AP173" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ173" t="n">
         <v>1</v>
@@ -38407,7 +38407,7 @@
         <v>0.4</v>
       </c>
       <c r="AP174" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ174" t="n">
         <v>0.33</v>
@@ -39279,7 +39279,7 @@
         <v>0.45</v>
       </c>
       <c r="AP178" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ178" t="n">
         <v>0.67</v>
@@ -39500,7 +39500,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ179" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR179" t="n">
         <v>2.16</v>
@@ -39718,7 +39718,7 @@
         <v>2</v>
       </c>
       <c r="AQ180" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AR180" t="n">
         <v>1.5</v>
@@ -40151,10 +40151,10 @@
         <v>0.73</v>
       </c>
       <c r="AP182" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ182" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR182" t="n">
         <v>1.99</v>
@@ -40805,10 +40805,10 @@
         <v>0.82</v>
       </c>
       <c r="AP185" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ185" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR185" t="n">
         <v>1.64</v>
@@ -41677,7 +41677,7 @@
         <v>0.73</v>
       </c>
       <c r="AP189" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ189" t="n">
         <v>0.67</v>
@@ -43500,6 +43500,878 @@
       </c>
       <c r="BP197" t="n">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" t="n">
+        <v>7964639</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Serbia SuperLiga</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="n">
+        <v>46082.375</v>
+      </c>
+      <c r="F198" t="n">
+        <v>25</v>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Radnički Niš</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Javor Ivanjica</t>
+        </is>
+      </c>
+      <c r="I198" t="n">
+        <v>0</v>
+      </c>
+      <c r="J198" t="n">
+        <v>0</v>
+      </c>
+      <c r="K198" t="n">
+        <v>0</v>
+      </c>
+      <c r="L198" t="n">
+        <v>1</v>
+      </c>
+      <c r="M198" t="n">
+        <v>0</v>
+      </c>
+      <c r="N198" t="n">
+        <v>1</v>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>['73']</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q198" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R198" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S198" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="T198" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="U198" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="V198" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="W198" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X198" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Y198" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z198" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA198" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB198" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC198" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD198" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AE198" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AF198" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AG198" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AH198" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI198" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AJ198" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AK198" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AL198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM198" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AN198" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO198" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AP198" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ198" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AR198" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AS198" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AT198" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU198" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV198" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW198" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX198" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY198" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ198" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA198" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB198" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC198" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD198" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BE198" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF198" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BG198" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BH198" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BI198" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BJ198" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BK198" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BL198" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BM198" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BN198" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BO198" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="BP198" t="n">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" t="n">
+        <v>7964514</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Serbia SuperLiga</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="n">
+        <v>46082.47916666666</v>
+      </c>
+      <c r="F199" t="n">
+        <v>25</v>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Napredak</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Spartak Subotica</t>
+        </is>
+      </c>
+      <c r="I199" t="n">
+        <v>0</v>
+      </c>
+      <c r="J199" t="n">
+        <v>0</v>
+      </c>
+      <c r="K199" t="n">
+        <v>0</v>
+      </c>
+      <c r="L199" t="n">
+        <v>1</v>
+      </c>
+      <c r="M199" t="n">
+        <v>1</v>
+      </c>
+      <c r="N199" t="n">
+        <v>2</v>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>['90+3']</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>['55']</t>
+        </is>
+      </c>
+      <c r="Q199" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R199" t="n">
+        <v>2</v>
+      </c>
+      <c r="S199" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T199" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="U199" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="V199" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="W199" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X199" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="Y199" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z199" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA199" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB199" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC199" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD199" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AE199" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF199" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG199" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH199" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI199" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AJ199" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AK199" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AL199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM199" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN199" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AO199" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AP199" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AQ199" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AR199" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AS199" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AT199" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AU199" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV199" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW199" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX199" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY199" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ199" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA199" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB199" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC199" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD199" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BE199" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF199" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BG199" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BH199" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BI199" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BJ199" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BK199" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BL199" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BM199" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BN199" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BO199" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="BP199" t="n">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" t="n">
+        <v>7964638</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Serbia SuperLiga</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="n">
+        <v>46082.54166666666</v>
+      </c>
+      <c r="F200" t="n">
+        <v>25</v>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Radnički Kragujevac</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Red Star Belgrade</t>
+        </is>
+      </c>
+      <c r="I200" t="n">
+        <v>0</v>
+      </c>
+      <c r="J200" t="n">
+        <v>1</v>
+      </c>
+      <c r="K200" t="n">
+        <v>1</v>
+      </c>
+      <c r="L200" t="n">
+        <v>0</v>
+      </c>
+      <c r="M200" t="n">
+        <v>2</v>
+      </c>
+      <c r="N200" t="n">
+        <v>2</v>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>['3', '78']</t>
+        </is>
+      </c>
+      <c r="Q200" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R200" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S200" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="T200" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U200" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V200" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="W200" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X200" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y200" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z200" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA200" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB200" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC200" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD200" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="AE200" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF200" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AG200" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AH200" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AI200" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AJ200" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK200" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AL200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM200" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AN200" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO200" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AP200" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AQ200" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AR200" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AS200" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AT200" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="AU200" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV200" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW200" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX200" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY200" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ200" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA200" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB200" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC200" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD200" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="BE200" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="BF200" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BG200" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH200" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BI200" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ200" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BK200" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BL200" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BM200" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BN200" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BO200" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="BP200" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" t="n">
+        <v>7964625</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Serbia SuperLiga</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="n">
+        <v>46083.54166666666</v>
+      </c>
+      <c r="F201" t="n">
+        <v>25</v>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>IMT Novi Beograd</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Radnik Surdulica</t>
+        </is>
+      </c>
+      <c r="I201" t="n">
+        <v>0</v>
+      </c>
+      <c r="J201" t="n">
+        <v>0</v>
+      </c>
+      <c r="K201" t="n">
+        <v>0</v>
+      </c>
+      <c r="L201" t="n">
+        <v>0</v>
+      </c>
+      <c r="M201" t="n">
+        <v>0</v>
+      </c>
+      <c r="N201" t="n">
+        <v>0</v>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q201" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="R201" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="S201" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T201" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U201" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="V201" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="W201" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X201" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y201" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z201" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA201" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB201" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AC201" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD201" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE201" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF201" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AG201" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AH201" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI201" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AJ201" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AK201" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM201" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AN201" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO201" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AP201" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AQ201" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AR201" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS201" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AT201" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AU201" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW201" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX201" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY201" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ201" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA201" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB201" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC201" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD201" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BE201" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="BF201" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BG201" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BH201" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BI201" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BJ201" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BK201" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BL201" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BM201" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="BN201" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BO201" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="BP201" t="n">
+        <v>1.11</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Serbia SuperLiga_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Serbia SuperLiga_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP201"/>
+  <dimension ref="A1:BP203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ4" t="n">
         <v>0.67</v>
@@ -3312,7 +3312,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -3963,7 +3963,7 @@
         <v>3</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ16" t="n">
         <v>0.62</v>
@@ -5492,7 +5492,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR23" t="n">
         <v>2.76</v>
@@ -6797,7 +6797,7 @@
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ29" t="n">
         <v>1</v>
@@ -7018,7 +7018,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR30" t="n">
         <v>2.58</v>
@@ -8323,7 +8323,7 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ36" t="n">
         <v>1.69</v>
@@ -8977,7 +8977,7 @@
         <v>0.67</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ39" t="n">
         <v>0.33</v>
@@ -9634,7 +9634,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR42" t="n">
         <v>2.38</v>
@@ -10721,7 +10721,7 @@
         <v>0.33</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ47" t="n">
         <v>0.6899999999999999</v>
@@ -12247,7 +12247,7 @@
         <v>1</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ54" t="n">
         <v>0.67</v>
@@ -12904,7 +12904,7 @@
         <v>2</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR57" t="n">
         <v>1.6</v>
@@ -13337,7 +13337,7 @@
         <v>0.67</v>
       </c>
       <c r="AP59" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ59" t="n">
         <v>0.77</v>
@@ -13558,7 +13558,7 @@
         <v>2.58</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR60" t="n">
         <v>2.91</v>
@@ -16171,7 +16171,7 @@
         <v>0.2</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ72" t="n">
         <v>0.67</v>
@@ -16610,7 +16610,7 @@
         <v>2</v>
       </c>
       <c r="AQ74" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR74" t="n">
         <v>1.7</v>
@@ -16825,7 +16825,7 @@
         <v>2</v>
       </c>
       <c r="AP75" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ75" t="n">
         <v>1.33</v>
@@ -17046,7 +17046,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR76" t="n">
         <v>1.17</v>
@@ -19659,7 +19659,7 @@
         <v>0.5</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ88" t="n">
         <v>0.77</v>
@@ -20095,7 +20095,7 @@
         <v>2.6</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ90" t="n">
         <v>2.08</v>
@@ -20534,7 +20534,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR92" t="n">
         <v>1.17</v>
@@ -22496,7 +22496,7 @@
         <v>2</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR101" t="n">
         <v>1.7</v>
@@ -23147,7 +23147,7 @@
         <v>0.57</v>
       </c>
       <c r="AP104" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ104" t="n">
         <v>0.62</v>
@@ -23586,7 +23586,7 @@
         <v>2</v>
       </c>
       <c r="AQ106" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR106" t="n">
         <v>1.84</v>
@@ -23801,7 +23801,7 @@
         <v>0.43</v>
       </c>
       <c r="AP107" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ107" t="n">
         <v>0.33</v>
@@ -24673,7 +24673,7 @@
         <v>2.29</v>
       </c>
       <c r="AP111" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ111" t="n">
         <v>2.08</v>
@@ -26638,7 +26638,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR120" t="n">
         <v>1.78</v>
@@ -26856,7 +26856,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ121" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR121" t="n">
         <v>2.18</v>
@@ -27725,7 +27725,7 @@
         <v>2.29</v>
       </c>
       <c r="AP125" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ125" t="n">
         <v>2.23</v>
@@ -29469,7 +29469,7 @@
         <v>0.5</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ133" t="n">
         <v>0.77</v>
@@ -30126,7 +30126,7 @@
         <v>2.58</v>
       </c>
       <c r="AQ136" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR136" t="n">
         <v>2.67</v>
@@ -30341,7 +30341,7 @@
         <v>1.75</v>
       </c>
       <c r="AP137" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ137" t="n">
         <v>1.69</v>
@@ -30562,7 +30562,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ138" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR138" t="n">
         <v>1.66</v>
@@ -31652,7 +31652,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ143" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR143" t="n">
         <v>1.56</v>
@@ -33611,7 +33611,7 @@
         <v>2.11</v>
       </c>
       <c r="AP152" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ152" t="n">
         <v>2.23</v>
@@ -33832,7 +33832,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ153" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR153" t="n">
         <v>2.06</v>
@@ -34050,7 +34050,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ154" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR154" t="n">
         <v>1.48</v>
@@ -34265,7 +34265,7 @@
         <v>1.78</v>
       </c>
       <c r="AP155" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ155" t="n">
         <v>1.92</v>
@@ -35140,7 +35140,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ159" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR159" t="n">
         <v>1.38</v>
@@ -37099,7 +37099,7 @@
         <v>1.9</v>
       </c>
       <c r="AP168" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ168" t="n">
         <v>1.92</v>
@@ -37535,7 +37535,7 @@
         <v>0.9</v>
       </c>
       <c r="AP170" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ170" t="n">
         <v>1</v>
@@ -38628,7 +38628,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ175" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR175" t="n">
         <v>1.4</v>
@@ -39064,7 +39064,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ177" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR177" t="n">
         <v>1.23</v>
@@ -41026,7 +41026,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ186" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR186" t="n">
         <v>1.24</v>
@@ -42331,10 +42331,10 @@
         <v>1</v>
       </c>
       <c r="AP192" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ192" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR192" t="n">
         <v>1.62</v>
@@ -42549,7 +42549,7 @@
         <v>0.82</v>
       </c>
       <c r="AP193" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ193" t="n">
         <v>0.77</v>
@@ -44372,6 +44372,442 @@
       </c>
       <c r="BP201" t="n">
         <v>1.11</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" t="n">
+        <v>7964641</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Serbia SuperLiga</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="n">
+        <v>46088.375</v>
+      </c>
+      <c r="F202" t="n">
+        <v>26</v>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Bačka Topola</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Železničar Pančevo</t>
+        </is>
+      </c>
+      <c r="I202" t="n">
+        <v>0</v>
+      </c>
+      <c r="J202" t="n">
+        <v>0</v>
+      </c>
+      <c r="K202" t="n">
+        <v>0</v>
+      </c>
+      <c r="L202" t="n">
+        <v>0</v>
+      </c>
+      <c r="M202" t="n">
+        <v>0</v>
+      </c>
+      <c r="N202" t="n">
+        <v>0</v>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q202" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R202" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="S202" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T202" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U202" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="V202" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="W202" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X202" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Y202" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z202" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AA202" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AB202" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AC202" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD202" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AE202" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF202" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AG202" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH202" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI202" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AJ202" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK202" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL202" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM202" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AN202" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO202" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP202" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AQ202" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AR202" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS202" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AT202" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AU202" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV202" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW202" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX202" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY202" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ202" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA202" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB202" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC202" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD202" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BE202" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="BF202" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="BG202" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BH202" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BI202" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BJ202" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BK202" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BL202" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BM202" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BN202" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BO202" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="BP202" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" t="n">
+        <v>7964563</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Serbia SuperLiga</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="n">
+        <v>46088.45833333334</v>
+      </c>
+      <c r="F203" t="n">
+        <v>26</v>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Javor Ivanjica</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Čukarički</t>
+        </is>
+      </c>
+      <c r="I203" t="n">
+        <v>1</v>
+      </c>
+      <c r="J203" t="n">
+        <v>0</v>
+      </c>
+      <c r="K203" t="n">
+        <v>1</v>
+      </c>
+      <c r="L203" t="n">
+        <v>1</v>
+      </c>
+      <c r="M203" t="n">
+        <v>0</v>
+      </c>
+      <c r="N203" t="n">
+        <v>1</v>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>['45+2']</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q203" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="R203" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="S203" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="T203" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U203" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="V203" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="W203" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X203" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="Y203" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z203" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA203" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB203" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AC203" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD203" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE203" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AF203" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AG203" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AH203" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AI203" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AJ203" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK203" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL203" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM203" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN203" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AO203" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP203" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AQ203" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AR203" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AS203" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AT203" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AU203" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV203" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW203" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX203" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY203" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ203" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA203" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB203" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC203" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD203" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="BE203" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="BF203" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BG203" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BH203" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BI203" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BJ203" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BK203" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BL203" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BM203" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="BN203" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BO203" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="BP203" t="n">
+        <v>1.1</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Serbia SuperLiga_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Serbia SuperLiga_20252026.xlsx
@@ -44532,13 +44532,13 @@
         <v>1</v>
       </c>
       <c r="AW202" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX202" t="n">
         <v>5</v>
       </c>
       <c r="AY202" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ202" t="n">
         <v>6</v>
@@ -44753,13 +44753,13 @@
         <v>7</v>
       </c>
       <c r="AX203" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY203" t="n">
         <v>9</v>
       </c>
       <c r="AZ203" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA203" t="n">
         <v>2</v>
